--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N45_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N45_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.98411125485152</v>
+        <v>5.684918078913372</v>
       </c>
       <c r="D2" t="n">
-        <v>35.47012710691302</v>
+        <v>5.763895654873366</v>
       </c>
       <c r="E2" t="n">
-        <v>10.90852890823169</v>
+        <v>1.77263594758765</v>
       </c>
       <c r="F2" t="n">
-        <v>15.39068047033826</v>
+        <v>2.500985576429967</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.36488837961198</v>
+        <v>6.396794361686946</v>
       </c>
       <c r="D3" t="n">
-        <v>75.34418508092178</v>
+        <v>12.24343007564979</v>
       </c>
       <c r="E3" t="n">
-        <v>10.90852890823169</v>
+        <v>1.77263594758765</v>
       </c>
       <c r="F3" t="n">
-        <v>15.39068047033826</v>
+        <v>2.500985576429967</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>47.74970282192991</v>
+        <v>7.75932670856361</v>
       </c>
       <c r="D4" t="n">
-        <v>48.33367396342009</v>
+        <v>7.854222019055765</v>
       </c>
       <c r="E4" t="n">
-        <v>10.90852890823169</v>
+        <v>1.77263594758765</v>
       </c>
       <c r="F4" t="n">
-        <v>15.39068047033826</v>
+        <v>2.500985576429967</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.84256869545777</v>
+        <v>2.899417413011888</v>
       </c>
       <c r="D5" t="n">
-        <v>65.65439817712138</v>
+        <v>10.66883970378222</v>
       </c>
       <c r="E5" t="n">
-        <v>10.90852890823169</v>
+        <v>1.77263594758765</v>
       </c>
       <c r="F5" t="n">
-        <v>15.39068047033826</v>
+        <v>2.500985576429967</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
